--- a/data/data_availability.xlsx
+++ b/data/data_availability.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\farah.houdroge\Documents\GitHub\hcv-vaccine\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E7284035-3E4F-4525-BEEC-0605B2112898}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{88FD43BF-9B50-45AE-A9CE-8598C1AE3C67}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="38280" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{CF85D149-4197-4C81-8395-8E945CDAFAD3}"/>
   </bookViews>
@@ -417,7 +417,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -436,6 +436,13 @@
       <color rgb="FF000000"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="6">
@@ -542,10 +549,11 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="9" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -571,9 +579,11 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Percent" xfId="1" builtinId="5"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -905,7 +915,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{743F1145-74A6-4695-9C96-87F9E3F37112}">
-  <dimension ref="A1:G117"/>
+  <dimension ref="A1:G118"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="10" max="10" width="8.7265625" customWidth="1"/>
@@ -3600,6 +3610,32 @@
       </c>
       <c r="G117" s="5" t="s">
         <v>9</v>
+      </c>
+    </row>
+    <row r="118" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="B118" s="9">
+        <f>1-COUNTIF(B2:B117,"x")/ROWS(B2:B117)</f>
+        <v>0.67241379310344829</v>
+      </c>
+      <c r="C118" s="9">
+        <f t="shared" ref="C118:G118" si="0">1-COUNTIF(C2:C117,"x")/ROWS(C2:C117)</f>
+        <v>0.65517241379310343</v>
+      </c>
+      <c r="D118" s="9">
+        <f t="shared" si="0"/>
+        <v>0.76724137931034486</v>
+      </c>
+      <c r="E118" s="9">
+        <f t="shared" si="0"/>
+        <v>0.37931034482758619</v>
+      </c>
+      <c r="F118" s="9">
+        <f t="shared" si="0"/>
+        <v>0.25</v>
+      </c>
+      <c r="G118" s="9">
+        <f t="shared" si="0"/>
+        <v>0.62068965517241381</v>
       </c>
     </row>
   </sheetData>
@@ -3780,6 +3816,15 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
     <lcf76f155ced4ddcb4097134ff3c332f xmlns="460e4ad2-c64b-4f67-8552-094351f252e3">
@@ -3787,15 +3832,6 @@
     </lcf76f155ced4ddcb4097134ff3c332f>
   </documentManagement>
 </p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -3817,6 +3853,14 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{75AE4913-E6BC-4DF3-9CD5-CFB1EB35C566}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3CC92CD2-0CAB-46DF-9CE6-1C3DDC5C2C4B}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
@@ -3824,12 +3868,4 @@
     <ds:schemaRef ds:uri="460e4ad2-c64b-4f67-8552-094351f252e3"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{75AE4913-E6BC-4DF3-9CD5-CFB1EB35C566}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>